--- a/ALL/p13-out/Recipes.xlsx
+++ b/ALL/p13-out/Recipes.xlsx
@@ -1,37 +1,88 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Recipe</t>
+  </si>
+  <si>
+    <t>Generated At</t>
+  </si>
+  <si>
+    <t>easy pizza</t>
+  </si>
+  <si>
+    <t>Easy Pizza 🍕✨
+Ingredients:
+- 1 pre-made pizza crust
+- 1 cup pizza sauce
+- 1 ½ cups shredded mozzarella cheese
+- ½ cup sliced pepperoni
+- ¼ cup sliced bell peppers
+- ¼ cup sliced black olives
+- 1 teaspoon dried oregano
+Instructions:
+1. Preheat your oven to 450°F (232°C).
+2. Place the pre-made pizza crust on a baking sheet or pizza stone.
+3. Spread the pizza sauce evenly over the crust.
+4. Sprinkle the shredded mozzarella cheese over the sauce.
+5. Arrange the sliced pepperoni, bell peppers, and black olives on top of the cheese.
+6. Sprinkle the dried oregano over the toppings for added flavor.
+7. Bake in the preheated oven for 12-15 minutes, or until the cheese is bubbly and golden.
+8. Remove from the oven and let cool for a few minutes before slicing.
+9. Serve hot and enjoy your easy pizza!
+Prep Time: 10 minutes
+Cook Time: 15 minutes
+Total Time: 25 minutes
+Course: Main Course
+Cuisine: Italian
+Servings: 4
+Calories: ~280 per serving</t>
+  </si>
+  <si>
+    <t>2026-04-30 12:41:47</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +97,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,37 +413,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Recipe</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Generated At</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Json Recipe</t>
-        </is>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ALL/p13-out/Recipes.xlsx
+++ b/ALL/p13-out/Recipes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
   <si>
     <t>Title</t>
   </si>
@@ -23,6 +23,87 @@
   </si>
   <si>
     <t>Generated At</t>
+  </si>
+  <si>
+    <t>Json Recipe</t>
+  </si>
+  <si>
+    <t>Prompt</t>
+  </si>
+  <si>
+    <t>Prompt Image Ingredients</t>
+  </si>
+  <si>
+    <t>main_image</t>
+  </si>
+  <si>
+    <t>image_1</t>
+  </si>
+  <si>
+    <t>image_2</t>
+  </si>
+  <si>
+    <t>image_3</t>
+  </si>
+  <si>
+    <t>image_4</t>
+  </si>
+  <si>
+    <t>statu</t>
+  </si>
+  <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>main_image_ingredients</t>
+  </si>
+  <si>
+    <t>image_ing_1</t>
+  </si>
+  <si>
+    <t>image_ing_2</t>
+  </si>
+  <si>
+    <t>image_ing_3</t>
+  </si>
+  <si>
+    <t>image_ing_4</t>
+  </si>
+  <si>
+    <t>statu_ing</t>
+  </si>
+  <si>
+    <t>error_ing</t>
+  </si>
+  <si>
+    <t>pinterest_title</t>
+  </si>
+  <si>
+    <t>recipe_title_pin</t>
+  </si>
+  <si>
+    <t>pinterest_description</t>
+  </si>
+  <si>
+    <t>pinterest_keywords</t>
+  </si>
+  <si>
+    <t>_yoast_wpseo_focuskw</t>
+  </si>
+  <si>
+    <t>_yoast_wpseo_metadesc</t>
+  </si>
+  <si>
+    <t>_yoast_wpseo_keywordsynonyms</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>categories</t>
+  </si>
+  <si>
+    <t>pinterest_image</t>
   </si>
   <si>
     <t>easy pizza</t>
@@ -58,12 +139,147 @@
   <si>
     <t>2026-04-30 12:41:47</t>
   </si>
+  <si>
+    <t>{
+  "name": "easy pizza",
+  "summary": "This easy pizza recipe features a pre-made crust topped with pizza sauce, mozzarella cheese, and your choice of toppings. It's quick to prepare and perfect for a weeknight meal.",
+  "servings": "4",
+  "prep_time": "10",
+  "cook_time": "15",
+  "total_time": "25",
+  "calories": "280",
+  "course": "Main Course",
+  "cuisine": "Italian",
+  "keywords": [
+    "pizza",
+    "easy",
+    "quick",
+    "Italian",
+    "dinner"
+  ],
+  "notes": "Feel free to customize toppings to your liking. Calories are per serving.",
+  "ingredients": [
+    {
+      "amount": "1",
+      "unit": "pre-made pizza crust",
+      "name": "pizza crust"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "pizza sauce"
+    },
+    {
+      "amount": "1 ½",
+      "unit": "cups",
+      "name": "shredded mozzarella cheese"
+    },
+    {
+      "amount": "½",
+      "unit": "cup",
+      "name": "sliced pepperoni"
+    },
+    {
+      "amount": "¼",
+      "unit": "cup",
+      "name": "sliced bell peppers"
+    },
+    {
+      "amount": "¼",
+      "unit": "cup",
+      "name": "sliced black olives"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "dried oregano"
+    }
+  ],
+  "instructions": [
+    "Preheat your oven to 450°F (232°C).",
+    "Place the pre-made pizza crust on a baking sheet or pizza stone.",
+    "Spread the pizza sauce evenly over the crust.",
+    "Sprinkle the shredded mozzarella cheese over the sauce.",
+    "Arrange the sliced pepperoni, bell peppers, and black olives on top of the cheese.",
+    "Sprinkle the dried oregano over the toppings for added flavor.",
+    "Bake in the preheated oven for 12-15 minutes, or until the cheese is bubbly and golden.",
+    "Remove from the oven and let cool for a few minutes before slicing.",
+    "Serve hot and enjoy your easy pizza!"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>Realistic, appetizing ULTRA close-up of a freshly baked pizza topped with melted mozzarella cheese, pepperoni, bell peppers, and black olives, served in a clean white ceramic plate on a light neutral surface. Tight composition filling 90–100% of frame, clear food texture, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at the center of the pizza, slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>pizza crust, pizza sauce, mozzarella cheese, pepperoni, bell peppers, black olives, oregano, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0430122/b95e72d9c9d.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0430122/4ed5fde867a.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0430122/7b33aca7a57.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0430122/cb9271456d4.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0430122/9a513cf4e53.png</t>
+  </si>
+  <si>
+    <t>DONE</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0430122/41f8b348c00.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0430122/622a2ce362d.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0430122/ec3ad6b830e.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0430122/3966ab6d459.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0430122/40968a1014a.png</t>
+  </si>
+  <si>
+    <t>Quick and Easy Homemade Pizza Recipe for Delicious Family Nights</t>
+  </si>
+  <si>
+    <t>Quick and Delicious Homemade Pizza</t>
+  </si>
+  <si>
+    <t>Gather your family for a fun and delicious night with this quick and easy homemade pizza recipe. Using fresh mozzarella cheese and your favorite toppings like pepperoni, this Italian cuisine classic comes together in no time. Create lasting memories while enjoying a warm slice of pizza, made right in your kitchen.</t>
+  </si>
+  <si>
+    <t>easy pizza, homemade pizza, quick recipe, Italian cuisine, mozzarella cheese, pepperoni</t>
+  </si>
+  <si>
+    <t>Easy Pizza Recipe</t>
+  </si>
+  <si>
+    <t>Enjoy easy pizza night with our simple recipe! Quick to make and delicious, perfect for any occasion.</t>
+  </si>
+  <si>
+    <t>Simple Pizza Recipe, Quick Pizza Recipe, Effortless Pizza Recipe</t>
+  </si>
+  <si>
+    <t>dinner</t>
+  </si>
+  <si>
+    <t>C:\Users\leno\Documents\GitHub\PINTEREST\ALL\p13-out\output_images\image_1.jpg</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,6 +294,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -112,16 +335,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -414,10 +643,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -427,19 +656,187 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S2" t="s">
+        <v>41</v>
+      </c>
+      <c r="U2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC2">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
+      <c r="AD2" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1"/>
+    <hyperlink ref="H2" r:id="rId2"/>
+    <hyperlink ref="I2" r:id="rId3"/>
+    <hyperlink ref="J2" r:id="rId4"/>
+    <hyperlink ref="K2" r:id="rId5"/>
+    <hyperlink ref="N2" r:id="rId6"/>
+    <hyperlink ref="O2" r:id="rId7"/>
+    <hyperlink ref="P2" r:id="rId8"/>
+    <hyperlink ref="Q2" r:id="rId9"/>
+    <hyperlink ref="R2" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ALL/p13-out/Recipes.xlsx
+++ b/ALL/p13-out/Recipes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
   <si>
     <t>Title</t>
   </si>
@@ -76,203 +76,181 @@
     <t>error_ing</t>
   </si>
   <si>
-    <t>pinterest_title</t>
-  </si>
-  <si>
-    <t>recipe_title_pin</t>
-  </si>
-  <si>
-    <t>pinterest_description</t>
-  </si>
-  <si>
-    <t>pinterest_keywords</t>
-  </si>
-  <si>
-    <t>_yoast_wpseo_focuskw</t>
-  </si>
-  <si>
-    <t>_yoast_wpseo_metadesc</t>
-  </si>
-  <si>
-    <t>_yoast_wpseo_keywordsynonyms</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>categories</t>
-  </si>
-  <si>
-    <t>pinterest_image</t>
-  </si>
-  <si>
-    <t>easy pizza</t>
-  </si>
-  <si>
-    <t>Easy Pizza 🍕✨
+    <t>Crispy Oven Baked Chicken Tacos</t>
+  </si>
+  <si>
+    <t>Crispy Oven Baked Chicken Tacos 🌮🔥
 Ingredients:
-- 1 pre-made pizza crust
-- 1 cup pizza sauce
-- 1 ½ cups shredded mozzarella cheese
-- ½ cup sliced pepperoni
-- ¼ cup sliced bell peppers
-- ¼ cup sliced black olives
-- 1 teaspoon dried oregano
+- 1 lb ground chicken
+- 1 tablespoon olive oil
+- 1 teaspoon chili powder
+- 1 teaspoon cumin
+- 1 teaspoon garlic powder
+- 1 teaspoon onion powder
+- 1 teaspoon salt
+- 8 small corn tortillas
+- 1 cup shredded lettuce
+- 1 cup diced tomatoes
+- 1 cup shredded cheese (cheddar or Mexican blend)
+- 1/2 cup sour cream
+- Fresh cilantro for garnish (optional)
 Instructions:
-1. Preheat your oven to 450°F (232°C).
-2. Place the pre-made pizza crust on a baking sheet or pizza stone.
-3. Spread the pizza sauce evenly over the crust.
-4. Sprinkle the shredded mozzarella cheese over the sauce.
-5. Arrange the sliced pepperoni, bell peppers, and black olives on top of the cheese.
-6. Sprinkle the dried oregano over the toppings for added flavor.
-7. Bake in the preheated oven for 12-15 minutes, or until the cheese is bubbly and golden.
-8. Remove from the oven and let cool for a few minutes before slicing.
-9. Serve hot and enjoy your easy pizza!
+1. Preheat the oven to 400°F (200°C).
+2. In a large skillet, heat the olive oil over medium heat and add the ground chicken.
+3. Cook the chicken until browned, about 5-7 minutes, stirring occasionally.
+4. Add the chili powder, cumin, garlic powder, onion powder, and salt to the chicken, mixing well to combine.
+5. Place the corn tortillas on a baking sheet and spoon the chicken mixture evenly onto each tortilla.
+6. Top each taco with shredded cheese and bake in the preheated oven for 10-12 minutes, or until the cheese is melted and the tortillas are crispy.
+7. Remove from the oven and let cool slightly before adding lettuce and tomatoes on top.
+8. Serve with sour cream and garnish with fresh cilantro if desired.
 Prep Time: 10 minutes
-Cook Time: 15 minutes
-Total Time: 25 minutes
+Cook Time: 20 minutes
+Total Time: 30 minutes
 Course: Main Course
-Cuisine: Italian
+Cuisine: Mexican
 Servings: 4
-Calories: ~280 per serving</t>
-  </si>
-  <si>
-    <t>2026-04-30 12:41:47</t>
+Calories: ~450 per serving</t>
+  </si>
+  <si>
+    <t>2026-05-08 14:43:16</t>
   </si>
   <si>
     <t>{
-  "name": "easy pizza",
-  "summary": "This easy pizza recipe features a pre-made crust topped with pizza sauce, mozzarella cheese, and your choice of toppings. It's quick to prepare and perfect for a weeknight meal.",
+  "name": "Crispy Oven Baked Chicken Tacos",
+  "summary": "These crispy oven baked chicken tacos are a delicious and easy meal option. Perfectly seasoned ground chicken is baked in corn tortillas and topped with fresh ingredients.",
   "servings": "4",
   "prep_time": "10",
-  "cook_time": "15",
-  "total_time": "25",
-  "calories": "280",
+  "cook_time": "20",
+  "total_time": "30",
+  "calories": "450",
   "course": "Main Course",
-  "cuisine": "Italian",
+  "cuisine": "Mexican",
   "keywords": [
-    "pizza",
+    "tacos",
+    "chicken",
+    "oven baked",
     "easy",
-    "quick",
-    "Italian",
+    "Mexican",
     "dinner"
   ],
-  "notes": "Feel free to customize toppings to your liking. Calories are per serving.",
+  "notes": "Feel free to customize toppings based on your preference. Calories are per serving.",
   "ingredients": [
     {
       "amount": "1",
-      "unit": "pre-made pizza crust",
-      "name": "pizza crust"
+      "unit": "lb",
+      "name": "ground chicken"
+    },
+    {
+      "amount": "1",
+      "unit": "tablespoon",
+      "name": "olive oil"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "chili powder"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "cumin"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "garlic powder"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "onion powder"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "salt"
+    },
+    {
+      "amount": "8",
+      "unit": "small",
+      "name": "corn tortillas"
     },
     {
       "amount": "1",
       "unit": "cup",
-      "name": "pizza sauce"
-    },
-    {
-      "amount": "1 ½",
-      "unit": "cups",
-      "name": "shredded mozzarella cheese"
+      "name": "shredded lettuce"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "diced tomatoes"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "shredded cheese (cheddar or Mexican blend)"
     },
     {
       "amount": "½",
       "unit": "cup",
-      "name": "sliced pepperoni"
-    },
-    {
-      "amount": "¼",
-      "unit": "cup",
-      "name": "sliced bell peppers"
-    },
-    {
-      "amount": "¼",
-      "unit": "cup",
-      "name": "sliced black olives"
-    },
-    {
-      "amount": "1",
-      "unit": "teaspoon",
-      "name": "dried oregano"
+      "name": "sour cream"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Fresh cilantro for garnish (optional)"
     }
   ],
   "instructions": [
-    "Preheat your oven to 450°F (232°C).",
-    "Place the pre-made pizza crust on a baking sheet or pizza stone.",
-    "Spread the pizza sauce evenly over the crust.",
-    "Sprinkle the shredded mozzarella cheese over the sauce.",
-    "Arrange the sliced pepperoni, bell peppers, and black olives on top of the cheese.",
-    "Sprinkle the dried oregano over the toppings for added flavor.",
-    "Bake in the preheated oven for 12-15 minutes, or until the cheese is bubbly and golden.",
-    "Remove from the oven and let cool for a few minutes before slicing.",
-    "Serve hot and enjoy your easy pizza!"
+    "Preheat the oven to 400°F (200°C).",
+    "In a large skillet, heat the olive oil over medium heat and add the ground chicken.",
+    "Cook the chicken until browned, about 5-7 minutes, stirring occasionally.",
+    "Add the chili powder, cumin, garlic powder, onion powder, and salt to the chicken, mixing well to combine.",
+    "Place the corn tortillas on a baking sheet and spoon the chicken mixture evenly onto each tortilla.",
+    "Top each taco with shredded cheese and bake in the preheated oven for 10-12 minutes, or until the cheese is melted and the tortillas are crispy.",
+    "Remove from the oven and let cool slightly before adding lettuce and tomatoes on top.",
+    "Serve with sour cream and garnish with fresh cilantro if desired."
   ]
 }</t>
   </si>
   <si>
-    <t>Realistic, appetizing ULTRA close-up of a freshly baked pizza topped with melted mozzarella cheese, pepperoni, bell peppers, and black olives, served in a clean white ceramic plate on a light neutral surface. Tight composition filling 90–100% of frame, clear food texture, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at the center of the pizza, slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
-  </si>
-  <si>
-    <t>pizza crust, pizza sauce, mozzarella cheese, pepperoni, bell peppers, black olives, oregano, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0430122/b95e72d9c9d.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0430122/4ed5fde867a.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0430122/7b33aca7a57.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0430122/cb9271456d4.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0430122/9a513cf4e53.png</t>
+    <t>Realistic, appetizing ULTRA close-up of crispy oven baked chicken tacos, featuring golden brown tortillas filled with seasoned ground chicken, melted cheese, fresh shredded lettuce, and diced tomatoes, served in a clean white ceramic plate on a light neutral surface. Tight composition filling 90–100% of frame, clear food texture, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at the food center, slight 3/4 angle. Exclude people, hands, faces, text, logos, and packaging. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>ground chicken, olive oil, chili powder, cumin, garlic powder, onion powder, salt, corn tortillas, lettuce, tomatoes, cheese, sour cream, cilantro, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0508134/9bd6f5af68d.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0508134/9298d114431.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0508134/df6bba6b8be.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0508134/8314df8dd93.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0508134/98f4b529568.png</t>
   </si>
   <si>
     <t>DONE</t>
   </si>
   <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0430122/41f8b348c00.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0430122/622a2ce362d.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0430122/ec3ad6b830e.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0430122/3966ab6d459.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0430122/40968a1014a.png</t>
-  </si>
-  <si>
-    <t>Quick and Easy Homemade Pizza Recipe for Delicious Family Nights</t>
-  </si>
-  <si>
-    <t>Quick and Delicious Homemade Pizza</t>
-  </si>
-  <si>
-    <t>Gather your family for a fun and delicious night with this quick and easy homemade pizza recipe. Using fresh mozzarella cheese and your favorite toppings like pepperoni, this Italian cuisine classic comes together in no time. Create lasting memories while enjoying a warm slice of pizza, made right in your kitchen.</t>
-  </si>
-  <si>
-    <t>easy pizza, homemade pizza, quick recipe, Italian cuisine, mozzarella cheese, pepperoni</t>
-  </si>
-  <si>
-    <t>Easy Pizza Recipe</t>
-  </si>
-  <si>
-    <t>Enjoy easy pizza night with our simple recipe! Quick to make and delicious, perfect for any occasion.</t>
-  </si>
-  <si>
-    <t>Simple Pizza Recipe, Quick Pizza Recipe, Effortless Pizza Recipe</t>
-  </si>
-  <si>
-    <t>dinner</t>
-  </si>
-  <si>
-    <t>C:\Users\leno\Documents\GitHub\PINTEREST\ALL\p13-out\output_images\image_1.jpg</t>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0508140/81b84b8705f.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0508140/716f0ccc324.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0508140/6d62ed65267.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0508140/8ebfe06cf80.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0508140/64ffb3c605f.png</t>
   </si>
 </sst>
 </file>
@@ -643,10 +621,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -707,121 +685,61 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:20">
+      <c r="A2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="B2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="C2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="D2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="E2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="F2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
-      <c r="A2" t="s">
+      <c r="K2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" t="s">
+      <c r="L2" t="s">
         <v>31</v>
       </c>
-      <c r="C2" t="s">
+      <c r="N2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D2" t="s">
+      <c r="O2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E2" t="s">
+      <c r="P2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="L2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="S2" t="s">
-        <v>41</v>
-      </c>
-      <c r="U2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V2" t="s">
-        <v>48</v>
-      </c>
-      <c r="W2" t="s">
-        <v>49</v>
-      </c>
-      <c r="X2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC2">
-        <v>4</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/ALL/p13-out/Recipes.xlsx
+++ b/ALL/p13-out/Recipes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="64">
   <si>
     <t>Title</t>
   </si>
@@ -74,6 +74,54 @@
   </si>
   <si>
     <t>error_ing</t>
+  </si>
+  <si>
+    <t>Statut Article</t>
+  </si>
+  <si>
+    <t>article</t>
+  </si>
+  <si>
+    <t>article_title</t>
+  </si>
+  <si>
+    <t>id_article</t>
+  </si>
+  <si>
+    <t>pinterest_title</t>
+  </si>
+  <si>
+    <t>recipe_title_pin</t>
+  </si>
+  <si>
+    <t>pinterest_description</t>
+  </si>
+  <si>
+    <t>pinterest_keywords</t>
+  </si>
+  <si>
+    <t>_yoast_wpseo_focuskw</t>
+  </si>
+  <si>
+    <t>_yoast_wpseo_metadesc</t>
+  </si>
+  <si>
+    <t>_yoast_wpseo_keywordsynonyms</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>categories</t>
+  </si>
+  <si>
+    <t>pinterest_image</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>post_url</t>
   </si>
   <si>
     <t>Crispy Oven Baked Chicken Tacos</t>
@@ -129,9 +177,9 @@
     "tacos",
     "chicken",
     "oven baked",
-    "easy",
+    "crispy",
     "Mexican",
-    "dinner"
+    "easy meal"
   ],
   "notes": "Feel free to customize toppings based on your preference. Calories are per serving.",
   "ingredients": [
@@ -214,43 +262,181 @@
 }</t>
   </si>
   <si>
-    <t>Realistic, appetizing ULTRA close-up of crispy oven baked chicken tacos, featuring golden brown tortillas filled with seasoned ground chicken, melted cheese, fresh shredded lettuce, and diced tomatoes, served in a clean white ceramic plate on a light neutral surface. Tight composition filling 90–100% of frame, clear food texture, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at the food center, slight 3/4 angle. Exclude people, hands, faces, text, logos, and packaging. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
-  </si>
-  <si>
-    <t>ground chicken, olive oil, chili powder, cumin, garlic powder, onion powder, salt, corn tortillas, lettuce, tomatoes, cheese, sour cream, cilantro, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0508134/9bd6f5af68d.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0508134/9298d114431.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0508134/df6bba6b8be.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0508134/8314df8dd93.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0508134/98f4b529568.png</t>
+    <t>Realistic, appetizing ULTRA close-up of crispy oven baked chicken tacos arranged in a clean white ceramic plate, topped with shredded lettuce, diced tomatoes, melted cheese, and a dollop of sour cream, served on a light neutral surface. Tight composition filling 90–100% of frame, clear food texture, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at the center of the tacos, slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>ground chicken, olive oil, chili powder, cumin, garlic powder, onion powder, salt, corn tortillas, shredded lettuce, diced tomatoes, shredded cheese, sour cream, cilantro, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0509095/bad252a1808.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509095/98655d9a083.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509095/5ef4674f443.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509095/1e7ea5d4fc2.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509095/2f5a57d7a23.png</t>
   </si>
   <si>
     <t>DONE</t>
   </si>
   <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0508140/81b84b8705f.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0508140/716f0ccc324.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0508140/6d62ed65267.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0508140/8ebfe06cf80.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0508140/64ffb3c605f.png</t>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0509095/cae149c45b6.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509095/c8ce291682a.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509095/e45e1633ea7.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509095/5efb4e5c275.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509095/4afe5914943.png</t>
+  </si>
+  <si>
+    <t>DONE ARTICLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Crispy Oven Baked Chicken Tacos Recipe
+## Introduction
+Crispy Oven Baked Chicken Tacos offer a delightful twist on traditional tacos, blending the comforting warmth of baked flavors with the vibrant essence of Mexican cuisine. As flavors mingle and enhance, these tacos present an irresistible combination that caters to both comfort food enthusiasts and health-conscious eaters alike. Perfect for weeknight dinners or family gatherings, this dish is sure to become a favorite among family and friends.
+The use of ground chicken instead of beef or pork not only lightens the dish but also allows for a subtle, savory flavor that pairs beautifully with the spices. These tacos are then topped with fresh lettuce, juicy tomatoes, and melting cheese, leading to a satisfying crunch that is enjoyable to eat. Whether served at a casual get-together or on a cozy weeknight, Crispy Oven Baked Chicken Tacos deliver both taste and satisfaction.
+## Recipe Overview
+- Prep Time: 10 minutes
+- Cook Time: 20 minutes
+- Total Time: 30 minutes
+- Course: Main Course
+- Cuisine: Mexican
+- Servings: 4
+- Calories: ~450 per serving
+## Ingredients
+- 1 lb ground chicken
+- 1 tablespoon olive oil
+- 1 teaspoon chili powder
+- 1 teaspoon cumin
+- 1 teaspoon garlic powder
+- 1 teaspoon onion powder
+- 1 teaspoon salt
+- 8 small corn tortillas
+- 1 cup shredded lettuce
+- 1 cup diced tomatoes
+- 1 cup shredded cheese (cheddar or Mexican blend)
+- 1/2 cup sour cream
+- Fresh cilantro for garnish (optional)
+{{image_ing_1}}
+## Instructions
+1. Preheat the oven to 400°F (200°C).
+2. In a large skillet, heat the olive oil over medium heat and add the ground chicken.
+3. Cook the chicken until browned, about 5-7 minutes, stirring occasionally.
+4. Add the chili powder, cumin, garlic powder, onion powder, and salt to the chicken, mixing well to combine.
+5. Place the corn tortillas on a baking sheet and spoon the chicken mixture evenly onto each tortilla.
+6. Top each taco with shredded cheese and bake in the preheated oven for 10-12 minutes, or until the cheese is melted and the tortillas are crispy.
+7. Remove from the oven and let cool slightly before adding lettuce and tomatoes on top.
+8. Serve with sour cream and garnish with fresh cilantro if desired.
+## Preparation Steps
+### Preheating the Oven
+To achieve the perfect crispy texture of the tortillas, it's crucial to preheat the oven to the right temperature of 400°F (200°C). This step ensures that as soon as the tacos are placed in the oven, they begin to crisp up immediately, creating a delicious contrast to the savory filling. Preheating is essential; without it, the tacos could end up being soggy rather than crispy.
+### Cooking the Chicken
+When it comes to preparing the filling for these tacos, the ground chicken is the star of the dish. Start by heating olive oil in a large skillet over medium heat. Once the oil is shimmering, add the ground chicken. Cook the chicken for about 5-7 minutes, stirring occasionally, until it’s uniformly browned and begins to release its savory aroma. The even coloration not only looks appealing but is indicative that the chicken is cooked through.
+Once the chicken is browned, it’s time to infuse it with flavor. Add in the chili powder, cumin, garlic powder, onion powder, and salt. These spices are the backbone of your taco filling, elevating the meal with their rich, smoky, and aromatic profiles. Mixing these into the cooked chicken ensures that every bite will be bursting with flavor. This step requires a good mix to evenly distribute the spices throughout the chicken, which is crucial for an explosion of taste in each taco.
+### Assembling the Tacos
+Once the chicken is flavorful and well-seasoned, it’s time to start assembling the tacos. Take your small corn tortillas and lay them flat on a baking sheet. With a spoon, carefully spoon the chicken mixture onto each tortilla, ensuring there is enough filling for a satisfying bite but leaving a little room for the toppings, which will elevate the flavor and texture. 
+After the chicken is evenly distributed among the tortillas, sprinkle shredded cheese generously over each taco. The cheese will melt during baking, becoming gooey and delicious, which complements the crunchy texture of the tortillas. The combination of the warm fillings and melted cheese creates a delightful layer of comfort that makes these tacos so enjoyable.
+## Baking Process
+Understanding the baking phase of these tacos is crucial for achieving the perfect texture and flavor. When ready, place the baking sheet in the preheated oven. Bake the tacos for approximately 10-12 minutes. During this time, the cheese will melt beautifully, and the edges of the tortillas will begin to crisp, providing that delightful crunch you seek in crispy tacos. 
+### Oven Settings
+Setting the oven temperature accurately is vital. At 400°F (200°C), the heat circulates adequately to achieve that crispy exterior while keeping the chicken filling moist and flavorful. This temperature strikes the right balance for both baking the tortillas and melting the cheese effectively.
+### Watching for Doneness
+It's essential to keep an eye on the tacos as they bake. The visual cues to look for include the cheese bubbling and the tortillas turning a light golden color. Once you observe these signs, it’s an indication that the tacos are ready to be taken out of the oven. Be cautious not to overbake, as this can lead to an overly crispy shell that is difficult to bite into.
+### Cooling Period
+Once the tacos are removed from the oven, let them cool slightly for a few minutes. This cooling period is important because it allows the cheese to set a bit, making it easier to top the tacos with fresh ingredients like shredded lettuce and diced tomatoes. Serving them immediately after baking may result in toppings slipping off, but allowing them to rest ensures that every bite is enjoyable and assembled well.
+## Serving Suggestions
+While these Crispy Oven Baked Chicken Tacos are delicious on their own, consider enhancing the experience with a few serving suggestions. Offering a variety of fresh toppings on the side can make a fun and interactive meal. In addition to the lettuce and tomatoes, try adding sliced jalapeños for some added heat, or some diced avocado for a creamy texture. You can also provide different salsas, like a fresh pico de gallo or a smoky chipotle sauce for those who like a little kick. 
+These customizable elements ensure that every diner can tailor their taco to their liking, adding a personal touch to each meal.
+### Fresh Toppings
+To truly elevate your Crispy Oven Baked Chicken Tacos, consider adding a variety of fresh toppings. Diced avocados are a fantastic option, offering a creamy texture that complements the crispy tortillas beautifully. Their subtle flavor adds richness to each bite. You might also consider including slices of jalapeños for those who enjoy a bit of heat. Fresh salsa, made from diced onions, tomatoes, cilantro, and lime juice, can provide an extra zing, enhancing the overall flavor profile of the dish. 
+Other topping suggestions include sliced radishes for a refreshing crunch, or pickled onions, which add an appealing tanginess. For those who enjoy a touch of sweetness, grilled corn can bring a pop of flavor that contrasts well with the savory chicken filling. Each addition not only improves taste but also adds visual appeal to your tacos.
+### Side Dishes
+To create a complete meal that complements your Crispy Oven Baked Chicken Tacos, consider serving them with traditional Mexican side dishes. Mexican rice is an excellent pairing, its fluffy texture soaked in flavors from spices and chicken broth, balancing out the flavors of the tacos nicely. Additionally, refried beans can provide a creamy, protein-rich contrast to the crunchy tacos. Black beans or pinto beans seasoned with spices can also be served on the side.
+Another option is to prepare a light salad with avocado, cucumber, and lime dressing. This refreshing side will enhance the meal by providing a fresh note that enhances the richness of the tacos. These side dishes are not only delicious but add variety to your dining experience.
+### Beverage Pairings
+Selecting the right beverages to accompany your Crispy Oven Baked Chicken Tacos can further enrich your meal. Traditional Mexican drinks like horchata offer a sweet, creamy flavor that pairs well with spicy food. This rice-based drink is refreshing and helps cool the palate after a bite of your tasty tacos. Another classic option is agua fresca, made from fresh fruit and water, which can be customized with flavors like watermelon or lime.
+For a more traditional experience, you might consider a Mexican beer such as Corona or Pacifico, both of which are light and crisp, making them ideal for balancing the richness of the cheese and the savory chicken. If you prefer non-alcoholic options, a classic limeade or even a simple iced tea can also work wonderfully.
+## Flavor Profile
+Exploring the flavor profile of Crispy Oven Baked Chicken Tacos reveals a delightful interplay of tastes and textures. The seasoned ground chicken provides a savory base enhanced by a mixture of spices. The blend of chili powder and cumin introduces warm and smoky notes, while the garlic and onion powders bring depth, making each taco flavorful and satisfying.
+### Spices and Seasonings
+The spices used in this dish greatly contribute to its appeal. Chili powder adds not just heat but also layers of flavor, while cumin lends an earthy taste that’s characteristic of Mexican cuisine. The balanced use of garlic and onion powder enhances the natural flavors of the ground chicken, making every bite delicious. The simplicity of these seasonings ensures that they work in harmony without overwhelming the palate.
+### Textural Contrast
+The textural contrast is a highlight of this dish. The baked corn tortillas of the tacos become wonderfully crispy in the oven, providing a satisfying crunch with each bite. In contrast, the ground chicken filling remains tender and juicy, creating an enjoyable juxtaposition. This combination of textures ensures that every taco offers an exciting mouthfeel, making them even more enjoyable.
+### Fresh Elements
+Lastly, the role of fresh vegetables like shredded lettuce and diced tomatoes is vital in balancing the flavors of the tacos. The crispness of the lettuce adds a refreshing crunch, while the tomatoes provide a sweet and juicy element that brightens the overall dish. Together, they enhance the flavor and add nutritional value, making the tacos not just delicious but also visually appealing.
+## Nutritional Information
+When preparing Crispy Oven Baked Chicken Tacos, it’s important to understand the nutritional benefits they provide. Each serving, around approximately 450 calories, is a great source of essential nutrients. 
+### Caloric Content
+With about 450 calories per serving, this hearty dish remains relatively moderate in caloric content while being satisfying enough to serve as a main course. By balancing rich ingredients with fresh toppings, it offers both indulgence and nutrition.
+### Protein and Fat Content
+The primary ingredient, ground chicken, is rich in protein, making these tacos a filling choice. Each serving provides enough protein to support energy and muscle health. Additionally, healthy fats come from olive oil and cheese, both of which contribute to overall satiety and flavor enhancement, allowing these tacos to not only be tasty but also nourishing.
+### Benefits of Fresh Ingredients
+Incorporating fresh ingredients like lettuce and tomatoes provides essential vitamins and minerals. Leafy greens not only add crunch but also contain vitamins A and C, promoting overall health. Tomoatoes are rich in antioxidants, adding to the nutritional profile of the meal. 
+## Storage and Reheating
+If you have leftovers of your Crispy Oven Baked Chicken Tacos, proper storage and reheating methods can help maintain flavor and texture.
+### Proper Storage Techniques
+To keep your cooked tacos fresh, you should store them in airtight containers in the refrigerator. It’s best to separate the taco filling from the tortillas to prevent the tortillas from becoming soggy. If you've made extra toppings, those should also be stored separately to maintain freshness.
+### Reheating Recommendations
+When reheating, you can place the tacos in a preheated oven at a low temperature to help maintain their crispiness. Wrapping them in aluminum foil can help keep them warm without drying out the filling. Alternatively, using a skillet over medium heat can also work well, allowing the tortillas to crisp up while warming through.
+## Variations and Adaptations
+Crispy Oven Baked Chicken Tacos are versatile and can be customized to fit various dietary needs or personal preferences.
+### Alternative Proteins
+If ground chicken isn't your preference, alternatives such as ground turkey, beef, or even plant-based meats can be used without altering the overall preparation process. Each protein will bring its unique flavor profile and texture to the dish. 
+### Vegetarian Version
+For a vegetarian-friendly adaptation, you could use beans, lentils, or even diced vegetables as the filling. These options can provide a substantial texture and flavor while keeping the dish nutritious and hearty.
+### Gluten-Free Options
+Those requiring a gluten-free option can easily do so by using corn tortillas specifically labeled as gluten-free. This way, you can enjoy the same delicious taco experience without worrying about gluten content.
+## Tips for Success
+Whether you’re a seasoned cook or a beginner, these helpful tips can guide you in making the best Crispy Oven Baked Chicken Tacos.
+### Avoiding Soggy Tortillas
+To prevent soggy tortillas, it's important to ensure that the tortilla filling is not over-sauced or too wet. Ensuring your chicken is well-cooked and not watery will help maintain the tortilla integrity during baking.
+### Cheese Selection
+Selecting the right cheese can significantly affect the flavor and texture of your tacos. Cheddar cheese adds a sharp flavor, while a Mexican blend can create a harmonious mix of tastes that complement the spices in the chicken.
+### Ensuring Even Cooking
+To ensure that the chicken cooks thoroughly, it’s advisable to break it up well in the skillet while browning. Ensuring the filling is evenly distributed among the tortillas before baking will also help achieve consistent cooking throughout.
+## Conclusion
+Crispy Oven Baked Chicken Tacos offer a delightful blend of flavors and textures that are both comforting and satisfying. The various ways to customize the dish and the health benefits derived from its fresh ingredients make it an appealing choice for many. This recipe is an excellent option for those seeking a delicious and quick meal ideal for any occasion.
+</t>
+  </si>
+  <si>
+    <t>Crispy Oven Baked Chicken Tacos Recipe</t>
+  </si>
+  <si>
+    <t>Crispy Oven Baked Chicken Tacos Recipe for a Delicious Mexican Meal</t>
+  </si>
+  <si>
+    <t>Crispy Chicken Tacos with Fresh Toppings</t>
+  </si>
+  <si>
+    <t>Savor the flavors of Mexican cuisine with these crispy oven-baked chicken tacos, perfect for a delicious and healthy dinner. This easy recipe features ground chicken and ensures a satisfying crunch in every bite. Enjoy a meal that brings the warmth and comfort of homemade cooking to your table.</t>
+  </si>
+  <si>
+    <t>oven baked tacos, ground chicken, crispy, easy recipe, Mexican cuisine, healthy dinner</t>
+  </si>
+  <si>
+    <t>Enjoy delicious crispy oven baked chicken tacos, an easy recipe perfect for family dinner or gatherings! 🌮🔥</t>
+  </si>
+  <si>
+    <t>Crunchy Baked Chicken Tacos, Crunchy Oven-Baked Chicken Tacos, Crispy Baked Chicken Tacos</t>
+  </si>
+  <si>
+    <t>dinner</t>
+  </si>
+  <si>
+    <t>C:\Users\leno\Documents\GitHub\PINTEREST\ALL\p13-out\output_images\image_1.jpg</t>
   </si>
 </sst>
 </file>
@@ -621,10 +807,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:AJ2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:36">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -685,61 +871,151 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:36">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="R2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U2" t="s">
+        <v>53</v>
+      </c>
+      <c r="V2" t="s">
+        <v>54</v>
+      </c>
+      <c r="W2" t="s">
+        <v>55</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC2" t="s">
         <v>36</v>
       </c>
-      <c r="S2" t="s">
-        <v>31</v>
+      <c r="AD2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AG2">
+        <v>4</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
